--- a/artfynd/A 34068-2022 artfynd.xlsx
+++ b/artfynd/A 34068-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34068-2022 artfynd.xlsx
+++ b/artfynd/A 34068-2022 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61722884</v>
+        <v>61722876</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -712,7 +707,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -722,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666007.4942946481</v>
+        <v>665992</v>
       </c>
       <c r="R2" t="n">
-        <v>6607781.685445307</v>
+        <v>6607457</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +750,9 @@
           <t>2016-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,32 +779,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61722876</v>
+        <v>61722884</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,7 +811,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -841,13 +821,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665991.8937562748</v>
+        <v>666007</v>
       </c>
       <c r="R3" t="n">
-        <v>6607456.841532916</v>
+        <v>6607782</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,19 +854,9 @@
           <t>2016-10-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34068-2022 artfynd.xlsx
+++ b/artfynd/A 34068-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61722876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61722884</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>